--- a/xiuxian配置表/indir/z_jineng.xlsx
+++ b/xiuxian配置表/indir/z_jineng.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="960" windowWidth="24300" windowHeight="11025" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="z_jineng" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="z_jineng_metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="z_jineng_rules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_jineng" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_jineng_metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="z_jineng_rules" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.25" customWidth="1" min="1" max="1"/>
@@ -780,16 +780,6 @@
           <t>specialPolicy</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>maxKnowledgeRequirements</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>maxRequirementLevel</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -872,16 +862,6 @@
           <t>specialPolicy</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>maxKnowledgeRequirements</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>maxRequirementLevel</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -960,16 +940,6 @@
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -996,505 +966,430 @@
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="n"/>
     </row>
     <row r="5" ht="27" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>knowledgeTreeConfigId</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>"dao_tree"</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>cultivationMethodConfigId</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>"xiulian_methods"</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="4" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="n"/>
     </row>
     <row r="7" ht="27" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>learningPolicy</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>"ability_config_knowledge_requirements"</t>
         </is>
       </c>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="n"/>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>effectFormula</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>"base with scalingMode and clamps"</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
+      <c r="C8" s="3" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="n"/>
+      <c r="P8" s="3" t="n"/>
     </row>
     <row r="9" ht="27" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>types</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>["combat_active","combat_passive","combat_upkeep","general_passive"]</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>["combat_active", "combat_passive", "combat_upkeep", "general_passive"]</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="n"/>
     </row>
     <row r="10" ht="27" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>generalPassivePolicy</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>"always_active_after_learning_same_stack_group_uses_highest"</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n"/>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
+      <c r="M10" s="3" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="n"/>
     </row>
     <row r="11" ht="27" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>combatPassivePolicy</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>"always_active_after_learning_combat_effects_only"</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="3" t="n"/>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>combatUpkeepPolicy</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>"manual_toggle_from_combat_skill_slot_while_active_pays_upkeep"</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n"/>
+      <c r="P12" s="3" t="n"/>
     </row>
     <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>combatUpkeepTogglePolicy</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n"/>
+      <c r="P13" s="3" t="n"/>
     </row>
     <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>combatActivePolicy</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>"cast_from_combat_skill_slot"</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-      <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="n"/>
+      <c r="P14" s="3" t="n"/>
     </row>
     <row r="15" ht="27" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>combatSkillSlotTypes</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>["combat_active","combat_upkeep"]</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-      <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="4" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>["combat_active", "combat_upkeep"]</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
+      <c r="P15" s="3" t="n"/>
     </row>
     <row r="16" ht="27" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>generalPassiveStackPolicy</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>"highest"</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
-      <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="4" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="n"/>
+      <c r="P16" s="3" t="n"/>
     </row>
     <row r="17" ht="27" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>effectCatalogConfigId</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>"effect_catalog"</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n"/>
-      <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="3" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="3" t="n"/>
+      <c r="O17" s="3" t="n"/>
+      <c r="P17" s="3" t="n"/>
     </row>
     <row r="18" ht="27" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>targetSelectionPolicy</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>current_selectable_enemy</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>current_selectable_enemy_only</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>protected_by_frontline_no_direct_target</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>backline_can_be_targeted_only_when_exposed_or_frontline_cleared</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>area_line_pierce_splash_domain_may_affect_backline_indirectly</t>
         </is>
       </c>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n"/>
-      <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
+      <c r="J18" s="3" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="3" t="n"/>
+      <c r="O18" s="3" t="n"/>
+      <c r="P18" s="3" t="n"/>
     </row>
     <row r="19" ht="27" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>specialActionControlPolicy</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>current_selectable_high_threat_enemy</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>delay_or_seal_next_special_action</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>hasPriorityEnemy</t>
         </is>
       </c>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
-      <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="n"/>
-    </row>
-    <row r="20" ht="27" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>learningKnowledgeGatePolicy</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>[1,2]</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>realm_only_no_knowledge_requirements</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="inlineStr">
-        <is>
-          <t>quality_3_or_above_may_require_knowledge</t>
-        </is>
-      </c>
-      <c r="Q20" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="27" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
